--- a/data/registrations.xlsx
+++ b/data/registrations.xlsx
@@ -132,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -141,6 +141,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -482,7 +485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -552,8 +555,9 @@
         <v>16</v>
       </c>
     </row>
+    <row r="3" ht="22" customHeight="1" s="4" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/data/registrations.xlsx
+++ b/data/registrations.xlsx
@@ -485,7 +485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -556,6 +556,7 @@
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" s="4" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="4" ht="22" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
